--- a/data/test_direct_listing.xlsx
+++ b/data/test_direct_listing.xlsx
@@ -566,12 +566,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>av_2171665897</t>
+          <t>av_2612385579</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Квартира-студия, 28 м², 1 кровать</t>
+          <t>Квартира-студия, 26,4 м², 2 кровати</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -580,19 +580,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>59.990242</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>30.292584</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3311</v>
+        <v>4015</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>0.2166666666666667</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -604,27 +604,27 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-14 17:10</t>
+          <t>2026-03-21 21:43</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>0;0;0;0;0;0;0;0;0;0;0;0;0;2900;3460;3560;2900;3680;2900;2900;2900;3800;2900;2900;3800;2900;2900;2900;2900;2900;3600;2900;2900;2900;2900;3600;2900;2900;2900;2900;2900;2900;2900;2900;2900;2900;4600;4900;2900;2900;2900;2900;5500;5500;2900;2900;2900;2900;5500;5500</t>
+          <t>2400;0;0;0;0;0;0;0;0;2500;2500;0;0;0;0;0;2800;3600;4100;4100;4100;4100;4100;4100;1640;4100;4100;4100;4100;1640;4100;4100;1640;4350;4240;4240;1640;4240;4240;4240;4240;4240;4240;4240;4240;4240;4240;4240;4240;4240;4240;4440;4640;4840;5040;5600;5600;5600;5600;5600</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1;1;1;1;1;1;1;1;1;1;1;1;1;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+          <t>0;1;1;1;1;1;1;1;1;0;0;1;1;1;1;1;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
-          <t>https://www.avito.ru/sankt-peterburg/kvartiry/kvartira-studiya_28_m_1_krovat_2171665897</t>
+          <t>https://www.avito.ru/sankt-peterburg/kvartiry/kvartira-studiya_264_m_2_krovati_2612385579</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-12 07:46</t>
+          <t>2026-04-13 14:16</t>
         </is>
       </c>
     </row>

--- a/data/test_direct_listing.xlsx
+++ b/data/test_direct_listing.xlsx
@@ -1,68 +1,154 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aleksander/Documents/Коды/my-poisk/avito/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_95DFDAB44A490C8DC4DB2924E712DE41417310E3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="44800" windowHeight="22840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аренда Avito" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Аренда Avito" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Аренда Avito'!$A$1:$O$2</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>ID объявления</t>
+  </si>
+  <si>
+    <t>Название</t>
+  </si>
+  <si>
+    <t>Категория жилья</t>
+  </si>
+  <si>
+    <t>Широта</t>
+  </si>
+  <si>
+    <t>Долгота</t>
+  </si>
+  <si>
+    <t>Средняя цена (руб./сут.)</t>
+  </si>
+  <si>
+    <t>Занятость (%)</t>
+  </si>
+  <si>
+    <t>Мин. срок (сут.)</t>
+  </si>
+  <si>
+    <t>Мгновенное бронирование</t>
+  </si>
+  <si>
+    <t>Рейтинг хоста</t>
+  </si>
+  <si>
+    <t>Последнее обновление хостом</t>
+  </si>
+  <si>
+    <t>Цены 60 дней</t>
+  </si>
+  <si>
+    <t>Календарь 60 дней</t>
+  </si>
+  <si>
+    <t>Ссылка</t>
+  </si>
+  <si>
+    <t>Дата снимка</t>
+  </si>
+  <si>
+    <t>av_2612385579</t>
+  </si>
+  <si>
+    <t>Квартира-студия, 26,4 м², 2 кровати</t>
+  </si>
+  <si>
+    <t>Студия</t>
+  </si>
+  <si>
+    <t>Да</t>
+  </si>
+  <si>
+    <t>2026-03-21 21:43</t>
+  </si>
+  <si>
+    <t>0;0;0;0;0;0;0;0;2500;2500;2500;2500;0;0;0;2800;3600;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4350;4240;4240;4240;4240;4240;4240;4240;4240;4240;1640;4240;4240;4240;4240;4240;4240;4240;4440;4640;4840;5040;5600;5600;5600;5600;5600;5600</t>
+  </si>
+  <si>
+    <t>1;1;1;1;1;1;1;1;0;0;0;0;1;1;1;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+  </si>
+  <si>
+    <t>https://www.avito.ru/sankt-peterburg/kvartiry/kvartira-studiya_264_m_2_krovati_2612385579</t>
+  </si>
+  <si>
+    <t>2026-04-14 07:56</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Calibri"/>
-      <sz val="10"/>
+      <family val="2"/>
     </font>
     <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0563C1"/>
       <name val="Calibri"/>
-      <color rgb="000563C1"/>
-      <sz val="10"/>
-      <u val="single"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
-        <bgColor rgb="00D9E2F3"/>
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor rgb="FFD9E2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,105 +161,55 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -461,177 +497,123 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="80" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
-    <col width="55" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="26" customWidth="1"/>
+    <col min="12" max="13" width="80" customWidth="1"/>
+    <col min="14" max="14" width="55" customWidth="1"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID объявления</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Название</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Категория жилья</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Широта</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Долгота</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Средняя цена (руб./сут.)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Занятость (%)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Мин. срок (сут.)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Мгновенное бронирование</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Рейтинг хоста</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Последнее обновление хостом</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Цены 60 дней</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Календарь 60 дней</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Ссылка</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Дата снимка</t>
-        </is>
+    <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>av_2612385579</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Квартира-студия, 26,4 м², 2 кровати</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Студия</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>59.990242</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>30.292584</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>4015</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>0.2166666666666667</v>
-      </c>
-      <c r="H2" s="2" t="n">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2">
+        <v>59.990242000000002</v>
+      </c>
+      <c r="E2" s="2">
+        <v>30.292584000000002</v>
+      </c>
+      <c r="F2" s="3">
+        <v>4169</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.18333333333333329</v>
+      </c>
+      <c r="H2" s="2">
         <v>2</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
+      <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2">
         <v>0</v>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-21 21:43</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>2400;0;0;0;0;0;0;0;0;2500;2500;0;0;0;0;0;2800;3600;4100;4100;4100;4100;4100;4100;1640;4100;4100;4100;4100;1640;4100;4100;1640;4350;4240;4240;1640;4240;4240;4240;4240;4240;4240;4240;4240;4240;4240;4240;4240;4240;4240;4440;4640;4840;5040;5600;5600;5600;5600;5600</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>0;1;1;1;1;1;1;1;1;0;0;1;1;1;1;1;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>https://www.avito.ru/sankt-peterburg/kvartiry/kvartira-studiya_264_m_2_krovati_2612385579</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-13 14:16</t>
-        </is>
+      <c r="K2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O2"/>
+  <autoFilter ref="A1:O2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/test_direct_listing.xlsx
+++ b/data/test_direct_listing.xlsx
@@ -1,154 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aleksander/Documents/Коды/my-poisk/avito/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_95DFDAB44A490C8DC4DB2924E712DE41417310E3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="44800" windowHeight="22840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Аренда Avito" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аренда Avito" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Аренда Avito'!$A$1:$O$2</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>ID объявления</t>
-  </si>
-  <si>
-    <t>Название</t>
-  </si>
-  <si>
-    <t>Категория жилья</t>
-  </si>
-  <si>
-    <t>Широта</t>
-  </si>
-  <si>
-    <t>Долгота</t>
-  </si>
-  <si>
-    <t>Средняя цена (руб./сут.)</t>
-  </si>
-  <si>
-    <t>Занятость (%)</t>
-  </si>
-  <si>
-    <t>Мин. срок (сут.)</t>
-  </si>
-  <si>
-    <t>Мгновенное бронирование</t>
-  </si>
-  <si>
-    <t>Рейтинг хоста</t>
-  </si>
-  <si>
-    <t>Последнее обновление хостом</t>
-  </si>
-  <si>
-    <t>Цены 60 дней</t>
-  </si>
-  <si>
-    <t>Календарь 60 дней</t>
-  </si>
-  <si>
-    <t>Ссылка</t>
-  </si>
-  <si>
-    <t>Дата снимка</t>
-  </si>
-  <si>
-    <t>av_2612385579</t>
-  </si>
-  <si>
-    <t>Квартира-студия, 26,4 м², 2 кровати</t>
-  </si>
-  <si>
-    <t>Студия</t>
-  </si>
-  <si>
-    <t>Да</t>
-  </si>
-  <si>
-    <t>2026-03-21 21:43</t>
-  </si>
-  <si>
-    <t>0;0;0;0;0;0;0;0;2500;2500;2500;2500;0;0;0;2800;3600;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4350;4240;4240;4240;4240;4240;4240;4240;4240;4240;1640;4240;4240;4240;4240;4240;4240;4240;4440;4640;4840;5040;5600;5600;5600;5600;5600;5600</t>
-  </si>
-  <si>
-    <t>1;1;1;1;1;1;1;1;0;0;0;0;1;1;1;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
-  </si>
-  <si>
-    <t>https://www.avito.ru/sankt-peterburg/kvartiry/kvartira-studiya_264_m_2_krovati_2612385579</t>
-  </si>
-  <si>
-    <t>2026-04-14 07:56</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <u/>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
       <sz val="10"/>
-      <color rgb="FF0563C1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF4472C4"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E2F3"/>
-        <bgColor rgb="FFD9E2F3"/>
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -161,55 +75,105 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -497,123 +461,177 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="26" customWidth="1"/>
-    <col min="12" max="13" width="80" customWidth="1"/>
-    <col min="14" max="14" width="55" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="12" max="12"/>
+    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID объявления</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Категория жилья</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Широта</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Долгота</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Средняя цена (руб./сут.)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Занятость (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Мин. срок (сут.)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Мгновенное бронирование</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Рейтинг хоста</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Последнее обновление хостом</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Цены 60 дней</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Календарь 60 дней</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Ссылка</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Дата снимка</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>av_2612385579</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Квартира-студия, 26,4 м², 2 кровати</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Студия</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>59.990242</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>30.292584</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>4150</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="2">
-        <v>59.990242000000002</v>
-      </c>
-      <c r="E2" s="2">
-        <v>30.292584000000002</v>
-      </c>
-      <c r="F2" s="3">
-        <v>4169</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0.18333333333333329</v>
-      </c>
-      <c r="H2" s="2">
-        <v>2</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>23</v>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21 21:43</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>0;0;0;0;0;0;0;0;2500;2500;2500;0;0;0;0;2800;3600;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4100;4350;4240;4240;4240;4240;4240;4240;1640;1640;4240;4240;4240;4240;4240;4240;4240;4240;4240;4440;4640;4840;5040;5600;5600;5600;5600;5600;5600</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>1;1;1;1;1;1;1;1;0;0;0;1;1;1;1;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0;0</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.avito.ru/sankt-peterburg/kvartiry/kvartira-studiya_264_m_2_krovati_2612385579</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14 15:18</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:O2"/>
   <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
